--- a/TEST_Excel_Export.xlsx
+++ b/TEST_Excel_Export.xlsx
@@ -75,7 +75,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -467,18 +467,18 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -542,7 +542,8 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="6"/>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>#</t>
@@ -750,8 +751,8 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -761,6 +762,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -797,6 +799,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>

--- a/TEST_Excel_Export.xlsx
+++ b/TEST_Excel_Export.xlsx
@@ -80,7 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -467,19 +469,19 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -751,8 +753,8 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
